--- a/r5-TC-FHIR-AG-Scheduling-R5-127-78---adapt-description-for-scheduling-server/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-127-78---adapt-description-for-scheduling-server/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T19:17:42+00:00</t>
+    <t>2026-02-25T08:56:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-TC-FHIR-AG-Scheduling-R5-127-78---adapt-description-for-scheduling-server/StructureDefinition-at-scheduling-slot.xlsx
+++ b/r5-TC-FHIR-AG-Scheduling-R5-127-78---adapt-description-for-scheduling-server/StructureDefinition-at-scheduling-slot.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T08:56:55+00:00</t>
+    <t>2026-02-25T09:54:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
